--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71CE880-4F7A-4B64-8469-876820648532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AB063C-92A5-4AEF-9237-3EA99774800A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -1992,1041 +1992,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>📁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> __pycache__ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>フォルダの概要と解説</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>概要と役割</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-__pycache__ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>は、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Python </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>インタプリタ（この環境では</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Python 3.12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）がソースコード（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）を実行・インポートする際に自動生成するコンパイル済みバイトコード（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.pyc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）を格納するキャッシュフォルダです。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>目的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>次回の実行時に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Python </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ソースコードの構文解析（コンパイル）処理を省き、モジュールの読み込み速度・起動スピードを向上させるために機能します。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>自動管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ソースコード（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）が更新されると、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Python </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>がタイムスタンプを検知して自動的に最新の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> .pyc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ファイルへ再生成します。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>現在のフォルダー内容</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>現在、このフォルダ内には以下のファイルが格納されています：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-main.cpython-312.pyc
- (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>サイズ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3.3 KB)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>プロジェクト直下の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 
-main.py
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Python 3.12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>環境で実行・インポートした際に生成されたバイトコードキャッシュです。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>コードレビュー・運用評価</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>評価項目</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>判定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>評価内容</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Git </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>バージョン管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>適正</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	
- .gitignore
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>行目に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> __pycache__/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>および</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> *.pyc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>が登録されており、リポジトリへ無駄なバイナリがコミットされないよう適切に保護されています。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>セキュリティ・機密性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>適正</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	.pyc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ファイルは簡単な逆コンパイルが可能ですが、参照元の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> main.py </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>内にハードコードされた秘密鍵やトークンは存在せず環境変数化されているため、キャッシュからの情報漏洩リスクもありません。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ファイル構成の健全性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>健全</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>キャッシュの蓄積や肥大化はなく、最新の起動結果のみが保持されています。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>運用上の注意点・メンテナンス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-__pycache__ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>フォルダは一時的に削除しても、次回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Python </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>実行時に自動生成されるため安全に削除可能です。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>キャッシュを強制クリアしたい場合は、以下のコマンド等で一括削除できます：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-powershell
-# PowerShell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>でのキャッシュクリア例</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Get-ChildItem -Path . -Recurse -Filter "__pycache__" | Remove-Item -Recurse -Force</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\backups</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -9258,6 +8223,2958 @@
   </si>
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\db</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">db/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダの概要と解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>概要と目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+db/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダは、本アプリケーションのランタイム・データベーススキーマのマイグレーション（テーブル定義変更履歴・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDL SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を管理するディレクトリです。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マイグレーション実行スクリプト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+scripts/manage_db_migrations.py
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と連携し、ローカル開発・テスト用の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQLite </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と本番・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>用の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Supabase / PostgreSQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の双方でスキーマの整合性を保ちながらバージョン管理を行っています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ディレクトリ構成と主要ファイル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ガイドライン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (
+db/migrations/README.md
+)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マイグレーション運用のルールが厳格に定義されています：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>イミュータブル運用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>共有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に適用済みのマイグレーションは変更せず、修正時は新たな前進マイグレーション（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Forward-fix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を追加する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>命名規約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: YYYYMMDDHHMMSS_short_slug.sql (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 20260618000000_sales_email_matching_schema.sql)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>事前検証</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コミット前に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> python scripts/manage_db_migrations.py validate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>および</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> --dry-run </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>で動作を事前確認する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🗄️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マイグレーションスクリプト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (db/migrations/)
+sqlite/
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ローカル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQLite (data/mighty.db </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>やテスト環境</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> data_test/) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>向け</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DDL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプト。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+20260614000000_app_core_schema.sql (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コアテーブル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: engineers, jobs, matches)
+20260616000000_feedback_events.sql (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フィードバックログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+20260616000001_support_requests.sql (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>問い合わせ管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+20260618000000_sales_email_matching_schema.sql (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メールパース・マッチングテーブル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+postgres/
+: Supabase / PostgreSQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>方言に適合した同一バージョン・同等構造の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DDL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプト。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+rollback/
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>万が一の本番障害時やスキーマ巻き戻し用の切り戻し用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプト。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>他のマイグレーションフォルダとの役割分担</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクトでは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定義が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>つのフォルダで役割分担されています：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>主な対象と管理内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+db/migrations/ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本フォルダ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アプリケーション層テーブル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: FastAPI / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプトから直接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>される業務テーブル群。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+supabase/migrations/	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>インフラ・セキュリティ層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: Supabase CLI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>により管理される</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RLS (Row Level Security) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ポリシー、認証</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Auth)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">pgvector </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>拡張など。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コードレビュー・運用評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価項目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>判定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スキーマ漂流の防止</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Schema Drift Protection)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>極めて優良</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>同一のバージョン番号で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sqlite/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> postgres/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の両</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DDL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が保持されており、ローカルテスト環境と本番環境でのスキーマ乖離が発生しない設計です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用ガバナンス・安全性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>優良</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	README.md </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>にて適用済みファイルの変更禁止や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> --dry-run </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>必須化がルール化され、管理スクリプト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> manage_db_migrations.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>でコマンド自動化されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ロールバック（切り戻し）対応</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>優良</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	rollback/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ディレクトリに削除・復旧用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプトを用意しておくことで、リリース時のダウンタイムや障害発生のリスクが最小化されています。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> __pycache__ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダの概要と解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>概要と役割</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+__pycache__ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>インタプリタ（この環境では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Python 3.12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）がソースコード（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を実行・インポートする際に自動生成するコンパイル済みバイトコード（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.pyc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を格納するキャッシュフォルダです。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>次回の実行時に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ソースコードの構文解析（コンパイル）処理を省き、モジュールの読み込み速度・起動スピードを向上させるために機能します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自動管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ソースコード（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）が更新されると、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>がタイムスタンプを検知して自動的に最新の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> .pyc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ファイルへ再生成します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現在のフォルダー内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現在、このフォルダ内には以下のファイルが格納されています：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+main.cpython-312.pyc
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サイズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3.3 KB)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プロジェクト直下の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+main.py
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Python 3.12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>環境で実行・インポートした際に生成されたバイトコードキャッシュです。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コードレビュー・運用評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価項目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>判定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Git </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>バージョン管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>適正</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	
+ .gitignore
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行目に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> __pycache__/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>および</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> *.pyc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が登録されており、リポジトリへ無駄なバイナリがコミットされないよう適切に保護されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セキュリティ・機密性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>適正</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	.pyc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ファイルは簡単な逆コンパイルが可能ですが、参照元の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> main.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>内にハードコードされた秘密鍵やトークンは存在せず環境変数化されているため、キャッシュからの情報漏洩リスクもありません。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ファイル構成の健全性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>健全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>キャッシュの蓄積や肥大化はなく、最新の起動結果のみが保持されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用上の注意点・メンテナンス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+__pycache__ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダは一時的に削除しても、次回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実行時に自動生成されるため安全に削除可能です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>キャッシュを強制クリアしたい場合は、以下のコマンド等で一括削除できます：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+powershell
+# PowerShell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>でのキャッシュクリア例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Get-ChildItem -Path . -Recurse -Filter "__pycache__" | Remove-Item -Recurse -Force</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例外処理</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 「例外処理（Exception Handling）」の解説
+例外処理とは、**「プログラムの実行中に発生する予期しないエラー（DB接続断、ネットワークタイムアウト、ファイル不整合、不正なユーザー入力など）を捕捉（catch / except）し、プログラムの強制終了（クラッシュ）を防いで安全にエラー制御・回復・通知を行うプログラミング構造および設計方針」**を指します。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な例外処理方針と品質ルール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エラー握りつぶし・無症状パッチの厳禁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+try-except </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>でエラーを無視して空のデータを返したり、サイレントに飲み込む修正（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Superficial Symptom Patches</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を明確に禁止。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Fail-closed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>原則の徹底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>認証失敗や予期せぬ例外が発生した場合、データを漏洩させず即座に安全側（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>503/401/403</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>遮断）へ倒す。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自動監査ガードによる網羅検証</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォームや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のエラーハンドリング（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>audit_form_error_handling.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管理画面のエラーハンドリング（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>audit_admin_dashboard_error_handling.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>診断フォールバックの透明性（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>audit_diagnosis_fallback_transparency.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9692,7 +11609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" ht="281.25" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -9702,8 +11619,11 @@
       <c r="D3" t="s">
         <v>0</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
@@ -9736,13 +11656,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
@@ -9754,14 +11674,15 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
       <c r="C7">
@@ -9769,21 +11690,28 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
+      <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
       <c r="C8">
         <f>C7+1</f>
         <v>6</v>
       </c>
       <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -9795,7 +11723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E9"/>
+  <dimension ref="B3:E10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -9845,7 +11773,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="202.5" x14ac:dyDescent="0.4">
@@ -9857,10 +11785,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="292.5" x14ac:dyDescent="0.4">
@@ -9872,10 +11800,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
@@ -9887,10 +11815,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="277.5" x14ac:dyDescent="0.4">
@@ -9902,10 +11830,25 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="281.25" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <f>C9+1</f>
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AB063C-92A5-4AEF-9237-3EA99774800A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E25A36-5D92-4B62-A261-C0D9A14BD155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
     <sheet name="用語集" sheetId="2" r:id="rId2"/>
+    <sheet name="YouTube" sheetId="3" r:id="rId3"/>
+    <sheet name="ブログ" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -11177,12 +11179,4861 @@
     </r>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">docs/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダの概要と解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>概要と目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+docs/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フォルダは、本プロジェクトにおける要件定義、システム設計書、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DevOps/SRE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用ランブック、役員会議資料、法的規約、障害ポストモーテム、およびナレッジグラフ索引が体系化された統合ドキュメントフォルダです。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単なるテキスト保管庫ではなく、自動監査スクリプト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">audit_docs_reference_integrity.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>など）や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> connect_knowledge_graph.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スクリプトによって、ドキュメント間の参照整合性とナレッジグラフが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 100% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自動保護されている点が最大の特徴です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>主要ドキュメントのカテゴリ構成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🕸️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ナレッジ基盤・インデックス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Knowledge Base)
+MASTER_KNOWLEDGE_GRAPH.md
+:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 266 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>件の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Markdown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Obsidian Vault </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や隠しフォルダ含む）を相互リンク接続し、孤立ノード（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Isolates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）および未解決リンク（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ghost Nodes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）をゼロに保つマスター索引起点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+DEVELOPMENT_KNOWLEDGE_FLOW.md
+:
+Antigravity / Claude / Codex </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>開発セッションから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NotebookLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Google Drive </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>へのナレッジ同期フロー仕様。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+HANDOVER_DOCUMENTATION_PACKAGE.md
+:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>システム引き継ぎ時に必要なドキュメント一式を網羅したパッケージ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>システム設計書・アーキテクチャ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Architecture &amp; Design)
+FIREBASE_SUPABASE_SYSTEM_ARCHITECTURE.md
+: Firebase Hosting / Cloud Functions + Supabase (PostgreSQL) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全体構成図。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+ARCHITECTURE_DECISION_RECORDS.md
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>技術選定の決定根拠（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ADR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+STRIPE_BILLING_INTEGRATION_DESIGN.md
+: Stripe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>決済・サブスクリプション設計。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SALES_EMAIL_AI_MATCHING_REQUIREMENTS.md
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>パース・マッチング要件定義。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🛠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用手順書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Runbooks)
+OPERATIONS_RUNBOOK_CATALOG.md
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全運用手順書の一覧カタログ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+PRODUCTION_ROLLBACK_RUNBOOK.md
+ / 
+DISASTER_RECOVERY_AND_ESCALATION_RUNBOOK.md
+SECRET_ROTATION_RUNBOOK.md
+ / 
+DB_MIGRATION_MANAGEMENT_RUNBOOK.md
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚖️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">D. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>法的リスク・規約・コンプライアンス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Legal &amp; Compliance)
+TERMS_OF_SERVICE.md
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>利用規約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>) / 
+PRIVACY_POLICY.md
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プライバシーポリシー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+TOKUSHOHO_NOTATION.md
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>特定商取引法に基づく表記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+LEGAL_REVIEW_SIGNOFF_TRACKER.md
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>弁護士レビュー管理台帳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>👔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">E. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>経営判定・役員会議</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (CEO Decisions &amp; Go/No-Go Packs)
+CEO_MEETING_AGENDA_*.md, CEO_PRESENTATION_DECISION_PACK_*.md
+PAID_LAUNCH_GO_NO_GO_DECISION_PACK_2026-07-24.md
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有料版ローンチ判定決定パック</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🛡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">F. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品質ガード</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ポストモーテム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Quality Guards &amp; Postmortems)
+QUALITY_GUARD_CATALOG.md
+ / 
+LANE_PREFLIGHT_GUARD.md
+POSTMORTEM_*.md (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>障害の原因分析と恒久対策の記録</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\docs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コードレビュー・運用評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価項目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>判定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>評価内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ナレッジグラフの完全性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Graph Connectivity)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 100% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>達成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	connect_knowledge_graph.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の自動生成により、全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 266 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ノードが相互接続され、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Obsidian Graph View </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>でも追跡可能なノード接続性が保証されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>参照整合性自動ガード</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Reference Integrity)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>極めて優良</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	audit_docs_reference_integrity.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>により、ドキュメント内のファイルリンク切れや古いパス参照がコミット前プリフライト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>run_lane_preflight.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）で検出・ガードされています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>網羅性とエンタープライズ品質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>圧倒的優良</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>設計・開発・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用・法務・経営決定・障害振り返りまでの全ライフサイクルが追跡可能な状態でドキュメント化されています。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\exports</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cloud Storage API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>☁️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 「Cloud Storage API」の解説
+Cloud Storage APIとは、**「Google Cloud が提供する高耐久・大容量のオブジェクトストレージサービス（Google Cloud Storage / GCS）に対して、ファイルやオブジェクトの保存・読み込み・削除・ライフサイクル管理・アクセス権制御などをプログラム（REST / gRPC / SDK）から実行するためのインターフェース」**を指します。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な活用場面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コールドストレージ・ログアーカイブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>長期保管が必要な監査ログやシステム実行ログを圧縮・自動保管（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">COLD_STORAGE_LOG_ARCHIVE_RUNBOOK.md </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>手順）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ナレッジ・ドキュメント連携</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+NotebookLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>および</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Google Drive </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>連携用のドキュメント一時保管・アップロード処理（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">scripts/upload_notebooklm_docs_to_drive.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>大容量データ・メディア管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>データベース（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>PostgreSQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）内に直接保持しない添付ファイルや各種エクスポートデータのストレージ層。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🤖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「機械学習（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Machine Learning / ML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機械学習とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「コンピュータが明示的なプログラミングなしに大量のデータからパターンや相互関係を自動的に学習し、未知のデータに対して分類・予測・評価・適応などの高次な判断を行う人工知能（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）技術の一分野」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機能の適用箇所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+POP3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>経由で取得した大量の営業案件メールとエンジニア人材プロファイルを言語モデル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）で解析し、適合度・マッチングスコアを自動抽出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内適性・モチベーション診断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>従業員の定型回答プロファイルから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>次元パラメータ（職務適合、意欲など）を分析・可視化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>勤怠・過重労働予測</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>勤務データや打刻記録のパターンから過重労働リスクや稼働インデックスを自動解析。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シラバス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「シラバス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Syllabus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>シラバスとは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「講義、研修コース、オンボーディングプログラムにおいて、学習目標、到達達成度、講義スケジュール、各回のテーマ、事前学習課題、評価方法などを体系的にまとめた講義・学習計画書」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な活用場面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エンジニア・リスキリング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スキル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bridge </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>研修</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内エンジニアのキャリアアップや新規技術（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>パイプライン、データ基盤等）習得のための研修シラバス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+docs/training/
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>内の各種ドキュメント）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プロジェクト開発者のオンボーディング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>新規参加メンバーが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>レーン開発体制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Antigravity, Codex, Claude Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）や品質ガード・運用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Runbook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のルールを円滑に習得するための講習ガイド。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Codex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZK3JhU73W18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Record &amp; Replay in Codex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可能です。英語の公式字幕を確認しました。ただし、リンク先動画の全文を逐語転載することはできないため、タイムスタンプ付きで内容をまとめます。
+[OpenAI公式「Record &amp; Replay in Codex」](https://www.youtube.com/watch?v=ZK3JhU73W18)（2分05秒）
+- **0:00–0:06**  
+  Codexに作業を実演すると、手順や好みを学習し、再利用できる「スキル」に変換できる。
+- **0:07–0:24**  
+  例としてYouTube公開作業を紹介。スプレッドシートからメタデータを取得し、素材を探し、YouTube Studioの項目を設定する一連の作業をCodexに記録させる。
+- **0:26–0:33**  
+  タイトルと説明文を入力し、サムネイルと英語字幕を追加。動画を非公開として保存する。
+- **0:48–1:00**  
+  Codexが操作記録を確認してスキル化。メタデータの場所、素材パッケージの構成、字幕追加・保存・確認方法を覚える。
+- **1:01–1:29**  
+  新しいタスクで次の動画パッケージを渡すと、Codexがスプレッドシートの該当行を特定し、メタデータ、サムネイル、字幕を設定。非公開でアップロードし、正しく保存されたか確認する。
+- **1:34–2:00**  
+  一度実演すれば、次回からCodexが同じ手順と好みを再現できる。動画公開だけでなく、PRの作成・共有方法やカレンダー招待の設定などにも応用可能。PC操作、ブラウザ操作、接続済みプラグインを組み合わせて実行できる。
+ご自身が権利を持つ動画であれば、動画・音声ファイルを添付いただければ、全文文字起こし、話者分け、日本語訳、SRT/VTT形式にもできます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Codexには、作業のやり方を一度見せるだけで、手順や好みを学習させることができます。
+さらに、学習した内容を、繰り返し利用できる「スキル」として保存できます。
+ここでは、YouTube動画を公開する作業を例に見てみましょう。
+動画を公開するときは、まず管理用のスプレッドシートから、タイトルや説明文などの情報を取得します。
+次に、対応する動画やサムネイル、字幕ファイルを探し、YouTube Studioの各項目を設定します。
+今回は、この一連の操作をCodexに見せながら進めます。
+タイトルと説明文を入力し、サムネイルと英語字幕を追加します。
+そして、動画を非公開の状態で保存します。
+作業が終わると、Codexが操作の記録を確認します。
+メタデータがどこに保存されているのか、素材がどのように整理されているのか、そして字幕の追加や保存、確認をどのように行うのかを学習し、ひとつのスキルにまとめます。
+次の動画では、新しいタスクを開いて素材一式を渡すだけです。
+Codexは、スプレッドシートから対応する情報を見つけ、タイトルや説明文を入力します。
+さらに、サムネイルと字幕を追加し、動画を非公開でアップロードします。
+最後に、すべての設定が正しく保存されたことまで確認します。
+このように、一度作業を見せれば、次回から同じ手順や好みをCodexが再現できます。
+動画の公開だけでなく、プルリクエストの作成や共有、カレンダーへの予定登録などにも応用できます。
+毎回すべての手順を説明する必要はありません。
+まず一度、あなたのやり方をCodexに見せてください。
+次からは、Codexがその作業を引き継いでくれます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コホート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「コホート（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cohort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コホートとは、「特定の時期にサービス登録したユーザーや、特定の共通属性・経験を持つユーザーでグループ化された分析対象集団（コホートグループ）」を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単一時点でのアクセス集計ではなく、時間経過に伴う利用継続率（リテンション率）、アクティブ率推移、離脱傾向、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**LTV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（顧客生涯価値）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>などを縦断的に分析する「コホート分析」で活用されます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な活用場面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>登録時期別コホート分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>月の社内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（社内本番公開）で使い始めたユーザーグループが、翌週・翌月にどの程度リピートして診断や営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を利用しているかの定着率分析。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>属性・プラン別コホート分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業部署・開発部署などの部門別コホートや、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Standard / Pro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>などの料金プラン別ユーザーグループごとの機能活用度追跡。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケティング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「マーケティング（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Marketing / GTM Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マーケティングとは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「顧客の潜在的・顕在的ニーズを発掘・獲得し、価値のあるプロダクトやサービスを届け、対価として継続的な事業収益や市場シェア拡大を獲得するための一連の戦略・市場調査・プライシング・プロモーション・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GTM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Go-To-Market</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）活動の全体像」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主なマーケティング展開要素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+GTM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>戦略（市場参入・成長戦略）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+GROWTH_STRATEGY_ROADMAP.md: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フェーズから一般有償</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公開に向けた成長ロードマップ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プライシング・料金プラン設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+docs/PRICING_PLAN_SPECIFICATION.md
+: Free / Standard / Pro / Enterprise </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プラン構成と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stripe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>連携。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>リード獲得・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+docs/landing-pages/: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>各顧客ターゲット層向けの集客ランディングページおよび訴求メッセージ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>価値訴求・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">North Star KPI:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「営業マッチング成約時間の削減率」を最重要価値指標として製品プロモーションを展開。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=08hgAtg-P_8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Codex for Solutions Engineers: Making AI Tangible for Customers</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スクリプト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIの価値を顧客へ伝えるには、機能説明より、相手の課題を具体的な体験に変えることが重要です。
+OpenAIのソリューションエンジニアは、Codexで顧客レビューを分析し、繰り返し挙がる不満や要望を整理します。
+その結果からウェブサイトの試作品を作り、改善後の体験をその場で見せます。顧客固有の問題を使うことで、AIの効果が自分ごとになります。
+さらに、うまくいった調査、分析、試作の流れは、スキルとして保存できます。一度成功した方法を、次の提案でも同じ品質で再利用できます。
+Codexはコードを書く道具だけではありません。課題を理解し、解決策を形にし、成功した方法を次の仕事へつなぐパートナーです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「シニアリティ・グラディエント（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Seniority Gradient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>シニアリティ・グラディエントとは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「組織や開発チーム、案件プロジェクトにおいて、メンバー間の経験年数・スキルレベル・職位権限の差（勾配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>グラディエント）によって生じるコミュニケーションの格差や心理的ハードルの度合い」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本概念の影響と本プロダクトでの重要性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>チームビルディングと心理的安全性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>勾配が大きすぎると、若手・ジュニア層が疑問点やトラブルを言いにくくなり（報告遅延）、シニア層が一方的な指示に偏るリスクが生じます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エンジニア＆案件フィット（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単に個人のスキル数値だけでなく、配属先チームの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>シニアリティ構成（フォロー体制・経験のバランス）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を可視化・最適化し、ミスマッチや過度な負担を防ぎます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内適性・モチベーション診断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>次元プロファイル解析を通じて、チーム内のコミュニケーション摩擦や心理的安全性の状態を定量的に捉える要素として扱われます。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シニアリティ・グラディエント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=u9zLlcsCDiQ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Build and test iOS apps without leaving Codex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Codexを使えば、SwiftUIアプリの実装、ビルド、テストを、ひとつの流れで進められます。
+プロジェクトを読み込み、スキームとシミュレータを確認。エックスコードビルドで、ビルドとテストを実行します。
+Codexは結果をもとに修正し、XcodeBuildMCPで、アプリの起動や画面確認まで自動化できます。
+小さな変更ごとに検証することが、iOS開発を安定させるポイントです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_jNbM8pV9oI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Codex as a Solutions Engineering Partner</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IMAP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルフォレンジック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>✉️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IMAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Internet Message Access Protocol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+IMAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「メールサーバー上にある電子メールメッセージにアクセス・参照・管理するための通信プロトコル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>RFC 3501</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">POP3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> IMAP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の違い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+POP3 (Post Office Protocol v3): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サーバーから電子メールを端末へダウンロードして保存（既定ではサーバーから消去されるか独立）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+IMAP: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>メール本体やフォルダ構造・未読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>既読フラグをサーバー側で一元管理・同期。複数端末（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PC, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スマホ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サーバー）から同一状態を維持しながらアクセス可能。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）での活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチング機能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+POP3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とともに、営業案件メール・エンジニア提案メールの取り込みプロトコルとして採用。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+IMAP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を使用することで、メールサーバー側の処理済みフラグやフォルダ分類とリアルタイムに同期しながら、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全件解析パイプライン（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）へ自動連携します。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>POP3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://learn.chatgpt.com/blog/custom-code-review-rules-for-codex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Custom Code Review rules for Codex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「デジタルフォレンジック（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Digital Forensics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>デジタルフォレンジックとは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「セキュリティインシデント（不正アクセス、情報漏洩、システム破壊等）の発生時や法的紛争において、デジタル機器・サーバー・ログ・ネットワーク通信から法的証拠性を保ったままデータを収集・保全・抽出・解析・記録する技術体系および調査手法」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主なセキュリティ・フォレンジック設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ログの完全性保護と改ざん防止監査</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+audit_security_log_integrity.py: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アクセスログや操作ログに個人情報・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>キーが露出していないか、ログ構造が完全かを自動監査。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+COLD_STORAGE_LOG_ARCHIVE_RUNBOOK.md: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>監査ログの長期間保全および改ざん不能なコールドストレージ自動アーカイブ運用。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>仮名化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Subject Pseudonym</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）による追跡性確保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生データや個人情報（氏名等）を自社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に保持せず、ハッシュ化・暗号化された仮名化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: onb-xxx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を用いて、事件発生時の監査追跡性（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Forensic Traceability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）とプライバシー保護を両立。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>インシデントポストモーテム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+INCIDENT_POSTMORTEM_RUNBOOK.md: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>障害・セキュリティ事案発生時のタイムライン特定および原因究明プロセス。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11223,6 +16074,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -11241,20 +16101,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -11587,7 +16457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02189A9A-9C55-4E7E-B1AE-F51A4A4AEC35}">
-  <dimension ref="B2:G8"/>
+  <dimension ref="B2:G10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -11631,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f>C3+1</f>
+        <f t="shared" ref="C4:C10" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -11652,7 +16522,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <f>C4+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D5" t="s">
@@ -11670,7 +16540,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <f>C5+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D6" t="s">
@@ -11686,7 +16556,7 @@
     </row>
     <row r="7" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
       <c r="C7">
-        <f>C6+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D7" t="s">
@@ -11701,8 +16571,11 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
       <c r="C8">
-        <f>C7+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="D8" t="s">
@@ -11715,6 +16588,33 @@
         <v>33</v>
       </c>
     </row>
+    <row r="9" spans="2:7" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11723,12 +16623,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E10"/>
+  <dimension ref="B3:E19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="105.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11751,7 +16651,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f>C3+1</f>
+        <f t="shared" ref="C4:C19" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -11766,7 +16666,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <f>C4+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D5" t="s">
@@ -11781,7 +16681,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <f>C5+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D6" t="s">
@@ -11796,7 +16696,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <f>C6+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D7" t="s">
@@ -11811,7 +16711,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <f>C7+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="D8" t="s">
@@ -11826,7 +16726,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <f>C8+1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="D9" t="s">
@@ -11841,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <f>C9+1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="D10" t="s">
@@ -11851,8 +16751,276 @@
         <v>38</v>
       </c>
     </row>
+    <row r="11" spans="2:5" ht="243.75" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="221.25" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="217.5" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="221.25" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="273.75" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="277.5" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="296.25" x14ac:dyDescent="0.4">
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFF1E46-B8F1-4111-9292-CB57C462E366}">
+  <dimension ref="A2:F6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="143.25" customWidth="1"/>
+    <col min="6" max="6" width="63.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="187.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B4">
+        <f>B3+1</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B5">
+        <f>B4+1</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B6">
+        <f>B5+1</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{C73E4B5E-2D09-4956-A933-CAF20540F0C6}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{42B3C306-0EC2-42DC-8AA0-09ED904D4645}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{4438B941-842E-45D5-9FD9-76DCFECAF728}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{CDA17EB9-E641-46C0-A290-D37769DB464E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3130DC33-D7DC-49CA-BAC6-4FF425438F8A}">
+  <dimension ref="A2:D3"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{20FCF3A0-8DB7-4003-ADB2-EB2C50EDDE30}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E25A36-5D92-4B62-A261-C0D9A14BD155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FA7342-29EE-4183-AAF1-2A777D3FA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
     <sheet name="用語集" sheetId="2" r:id="rId2"/>
-    <sheet name="YouTube" sheetId="3" r:id="rId3"/>
-    <sheet name="ブログ" sheetId="4" r:id="rId4"/>
+    <sheet name="OpenAIAcademy" sheetId="5" r:id="rId3"/>
+    <sheet name="YouTube" sheetId="3" r:id="rId4"/>
+    <sheet name="ブログ" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -16025,6 +16026,3220 @@
         <scheme val="minor"/>
       </rPr>
       <t>障害・セキュリティ事案発生時のタイムライン特定および原因究明プロセス。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RAG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.openai.com/learn/ai-foundations-juzjs/lessons</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Retrieval-Augmented Generation / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>検索拡張生成）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（検索拡張生成）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（大規模言語モデル）の持つ高い自然言語生成能力と、外部のデータベース・ナレッジベースからの高度な情報検索（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Retrieval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）機構を組み合わせるアーキテクチャ」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単体で発生しやすい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ハルシネーション（事実と異なる事実誤認や嘘の回答の生成）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を劇的に抑え、社内独自のドキュメントやリアルタイム・最新の情報をコンテキストとして注入することで、信頼性の高い正確な回答を提示できます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の基本プロセス（処理フロー）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>インデックス化（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Indexing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内文書・ナレッジ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Markdown, PDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）を短文ブロック（チャンク）に分割し、ベクトルエンベディングに変換してベクトルストアへ蓄積。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>関連情報検索（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Retrieval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ユーザーからの質問文をベクトル化し、意味的に最も関連性の高い文書チャンクを上位検索・抽出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回答生成（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Generation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>抽出した関連文書をプロンプト文脈（コンテキスト）として</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）に提示し、根拠のある回答を構成。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）での主な活用場所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人材データベースや案件要求要件の検索文脈を抽出し、適合度スコアリングと根拠テキストの自動抽出に活用。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+NotebookLM &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ナレッジ同期パイプライン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+scripts/sync_docs_to_notebooklm.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> docs/DEVELOPMENT_KNOWLEDGE_FLOW.md: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プロジェクト内の全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Runbook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・仕様書・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>WBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ナレッジベース化し、開発者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>QA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>応答や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>資料生成の基盤として利用。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>POP3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Post Office Protocol version 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+POP3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「電子メールサーバーに届いた電子メールを受信端末や自動解析プログラムへ一括ダウンロード・取り込みを行うための標準ネットワークプロトコル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>RFC 1939</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>特徴と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IMAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>との比較</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+POP3 (Post Office Protocol v3): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サーバーから未読メールをまとめてクライアント側に取得・保存して処理。ローカルでの保存・高速な一括読み込みに適しています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+IMAP (Internet Message Access Protocol): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サーバー上のメール本体やフォルダ状態（未読</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>既読）を複数端末でリアルタイム同期・参照します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）での活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチング機能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+SALES_EMAIL_INGESTION_POC_RUNBOOK.md / SALES_EMAIL_EXTRACTION_PIPELINE_RUNBOOK.md:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業担当メールアドレス宛に届く案件情報・技術者提案メールを、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>POP3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>経由で漏れなく全件自動抽出し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スコアリングパイプライン（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）へ安全に受け渡す基本通信規格として使用されています。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LLM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🧠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Large Language Model / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>大規模言語モデル）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「ペタバイト規模の莫大なテキストデータと深層学習（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>建築等）を用いて事前学習された、自然言語の理解、要約、翻訳、推論、コード生成、分類を高精度で行う人工知能（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）の基盤モデル」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>基盤モデルの採用（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Google Gemini </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>シリーズ）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+docs/GEMINI_MODEL_VERSION_MIGRATION_RUNBOOK.md / scripts/audit_gemini_model_policy.py:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高速・低コストな</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Gemini Flash </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や高精度・複雑推論向けの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Gemini Pro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1.5 / 2.0 / 3.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）を用途に応じて最適使い分け。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自然言語で送られる大量の非構造化メールから、スキル要件、稼働開始時期、契約条件、マッチングスコアを自動抽出・構造化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>適性・モチベーション診断の自動定性サマリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>次元パラメーターを言語化し、管理者・人事担当者向けの解説テキストや面談示唆を生成。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハーネス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🧪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「ハーネス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Test Harness / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テストハーネス）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テストハーネス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Harness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）とは、「プログラム、モジュール、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>モデル、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等を独立して自動実行・検証・評価するために、テスト対象を包み込んで入力データの供給、外部依存（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）のモック化、実行制御、結果の判定（アサーション）、証跡レポート出力を一括して担うテスト実行基盤・枠組み一式」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ハーネスの主な構成要素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テストドライバ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test Driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テスト対象を呼び出し、引数や擬似リクエストを投入する実行機構。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テストスタブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>モック（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mock / Stub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>外部依存（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stripe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>決済、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Google OAuth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Supabase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gemini API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）を擬似応答で代替し、環境に依存せずテストを完結させる仕組み。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アサーション・検証器（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Assertions &amp; Evaluators</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>出力結果が仕様通りの型・値・ステータスかを機械的に合否判定。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>証跡・メトリクス出力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実行結果や網羅率をレポート（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Markdown/JSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）として自動生成。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）での活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>レーン・プリフライト監査ハーネス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (scripts/run_lane_preflight.py):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>件の整合ガードと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スイート（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超のテストファイル）を一括実行し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>仮説（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）に基づきリポジトリ全体の健全性を瞬時に判定・証跡化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>契約テストハーネス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+audit_frontend_api_contract.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> audit_uat_api_coverage.py: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>フロントエンドとバックエンドの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>契約や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>仕様をモック</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ドライバ経由で自動検証。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セッション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏱️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「セッション（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セッションとは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「システム、通信、または開発運用において、開始から終了までの一連の継続的な処理単位・対話状態」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクトにおける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>つの重要文脈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・認証におけるセッション（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>User Auth Session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ユーザーがログインしてからログアウト（または有効期限切れ）するまでの認証継続状態。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Firebase Auth </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>により</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> JWT / ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>トークンが発行・管理され、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Supabase DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>へのアクセス制御（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>RLS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）に安全に引き継がれます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>開発運用におけるセッション（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dev / Agent Session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+AGENTS.md
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>で定義された</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回の開発作業単位。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セッション規約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>各セッションで最低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>件の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> WBS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>タスク（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>data/WBS.tsv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を完了し、終了前に必ずプリフライト監査（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>python scripts/run_lane_preflight.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を実行して作業ツリーの健全性（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>green</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を担保します。</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -16623,7 +19838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E19"/>
+  <dimension ref="B3:E23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -16651,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C19" si="0">C3+1</f>
+        <f t="shared" ref="C4:C23" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -16857,6 +20072,9 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="296.25" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -16868,13 +20086,79 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" ht="255" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
       <c r="C19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="D19" t="s">
         <v>72</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="367.5" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="333.75" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -16884,6 +20168,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
+  <dimension ref="D3"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="4" max="4" width="62.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D3" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{519012D9-D57E-4685-BBA6-CB1C8061383A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFF1E46-B8F1-4111-9292-CB57C462E366}">
   <dimension ref="A2:F6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -16987,7 +20293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3130DC33-D7DC-49CA-BAC6-4FF425438F8A}">
   <dimension ref="A2:D3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FA7342-29EE-4183-AAF1-2A777D3FA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3CFE07-1BCC-4497-99A2-4321FECC6901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -19240,6 +19240,514 @@
         <scheme val="minor"/>
       </rPr>
       <t>）を担保します。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SSOT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🏛️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Single Source of Truth / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>信頼できる唯一の情報源・単一正本）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**SSOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（単一正本）とは、「情報・データ・仕様の重複、乖離、不整合（データドリフト）を防ぐために、ある項目に関するすべての定義や状態を『唯一の正本（マスターデータ）』に集約・一元管理し、すべての参照先・下流システムがその正本のみを参照・同期するアーキテクチャおよび運用原則」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用の実例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+WBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>タスク管理の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SSOT:
+data/WBS.tsv: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プロジェクト全体の全タスクの単一正本。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+docs/WBS.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Google Sheets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（スプレッドシート）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Google Calendar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">GitHub Issues </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>はすべて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> data/WBS.tsv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>から一方向同期される下流アーティファクトとして扱われます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品質ガード登録の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SSOT:
+scripts/run_lane_preflight.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>内の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> GUARD_REGISTRY: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機械側正本。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+docs/QUALITY_GUARD_CATALOG.md
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>との完全一致が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> audit_guard_catalog.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>により常時監査されます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>用語・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>文言の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SSOT:
+docs/PROJECT_GLOSSARY.md
+ / docs/JAPANESE_UI_UX_STYLE_GUIDE.md: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>用語表記揺れ防止の単一正本。</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -19838,7 +20346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E23"/>
+  <dimension ref="B3:E24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -19866,7 +20374,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C23" si="0">C3+1</f>
+        <f t="shared" ref="C4:C24" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -20161,6 +20669,21 @@
         <v>85</v>
       </c>
     </row>
+    <row r="24" spans="2:5" ht="307.5" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3CFE07-1BCC-4497-99A2-4321FECC6901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BA0465-0B7F-4274-AE41-0C02F1337C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="94">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -19748,6 +19748,1270 @@
         <scheme val="minor"/>
       </rPr>
       <t>用語表記揺れ防止の単一正本。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブランチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「ブランチ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ブランチ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Git </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>などのバージョン管理システムにおいて、主要な開発ライン（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">main </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ブランチ等）から履歴を分岐させ、他の作業や本番環境に影響を与えることなく新機能の実装・バグ修正・実験的コードの検証を並行して進めるための独立した作業空間」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）におけるブランチ運用方針</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本番自動デプロイ先としての</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> main </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ブランチ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+main </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ブランチへのコミットやマージは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Firebase Hosting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mightylink-app.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）へ即座に自動デプロイされるプロダクション環境直結の基幹ブランチです。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>レーン・プリフライト監査による保護</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>レーン体制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Antigravity, Codex, Claude Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）がコードをプッシュ・マージする前に、必ずプリフライト監査（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>python scripts/run_lane_preflight.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を実行して</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>件の整合ガードと全自動テストスイートを合格（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>green</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）させることで、破損やドリフトのない健全な状態を維持します。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>worktree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SES</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>worktree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Git Worktree / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ワークツリー）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Git Worktree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とは、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「同一のローカル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>リポジトリ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を共有しながら、異なる複数のブランチを別の作業ディレクトリ（ワーキングツリー）として同時にチェックアウト・展開し、独立して並行作業・テスト・ビルドを実行できる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機能」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Worktree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の主な利点と特徴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>リポジトリの再クローン不要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ディスク容量やオブジェクト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を無駄に消費せず、数秒で独立した並行作業ディレクトリを作成可能。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>作業の中断・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>stash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・コンフリクト回避</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>進行中の作業を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> git stash </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>やコミットで退避させることなく、別ディレクトリで緊急のバグ修正や別機能のテストを並行して実行可能。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エージェント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サブエージェントのワークスペース分離</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>複数レーンやサブエージェント（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Antigravity, Codex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等）が、親ブランチの作業ツリーを汚染・競合することなく独立して安全にリサーチやコード修正を行う隔離基盤（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Workspace: 'share' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>モード等）として活用されます。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">System Engineering Service / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>システムエンジニアリングサービス）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**SES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（システムエンジニアリングサービス）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>業界における準委任契約形態のひとつであり、クライアント企業のプロジェクトやシステム開発に対して、エンジニアの技術力・労働力を継続的に提供・支援するサービス形態」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロダクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）との深い関わり</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>業界特有の課題（営業メールの山）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+SES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>業界では、毎日数千通規模で「案件募集メール」やパートナー企業からの「エンジニア提案メール（スキルシート）」が送受信され、営業担当者が目視で突き合わせ作業を行っています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マッチングによる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DX:
+docs/SALES_EMAIL_AI_MATCHING_REQUIREMENTS.md / SALES_EMAIL_INGESTION_POC_RUNBOOK.md:
+POP3/IMAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>経由で受信したメールを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Gemini LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が全件自動解析し、必要スキル・稼働時期・単価条件を即座に判定・スコアリング。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+North Star KPI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>である「営業マッチング成約時間の削減率」を劇的に改善する中核ターゲット領域となっています。</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -20346,7 +21610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E24"/>
+  <dimension ref="B3:E27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -20374,7 +21638,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C24" si="0">C3+1</f>
+        <f t="shared" ref="C4:C27" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -20684,6 +21948,51 @@
         <v>87</v>
       </c>
     </row>
+    <row r="25" spans="2:5" ht="240" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BA0465-0B7F-4274-AE41-0C02F1337C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D77A0B-E2F8-4D45-B63A-949C29728EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -21012,6 +21012,1148 @@
         <scheme val="minor"/>
       </rPr>
       <t>である「営業マッチング成約時間の削減率」を劇的に改善する中核ターゲット領域となっています。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.1 Welcome to AI Foundations</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yAbco3K_TLQ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YouTube投稿</t>
+    <rPh sb="7" eb="9">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NotebookLM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AGI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Artificial General Intelligence / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>汎用人工知能）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**AGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（汎用人工知能）とは、「特定の限定タスク（画像分類、チェス、単一のメール解析等）のみを処理する特化型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ANI: Narrow AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）とは異なり、人間と同等またはそれ以上の水準で、多種多様な知的活動、文脈横断の自律的推論、新規課題の学習・問題解決を汎用的に行える人工知能」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>特化型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ANI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の違い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+ANI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Artificial Narrow AI / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>特化型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定義された単一ドメインに特化（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>営業メール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のスキル抽出、勤怠データの過重労働スコア計算）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（汎用人工知能）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未知の環境や多領域の課題に対して自律的に思考・適応し、複数ツールの連携やソフトウェア開発・組織判断を総合的に遂行。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における位置づけと将来展望</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エージェント協調開発体制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現在は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Gemini LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Antigravity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Codex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Claude Code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等の自律サブエージェントが連携し、コード生成・ドキュメント監査・自動修正を自律協調で遂行。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プラットフォームの将来展望（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GROWTH_STRATEGY_ROADMAP.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単なるメールマッチングツールから、エンジニアのキャリア形成、適性・モチベーション診断、プロジェクトアサインを包括的・自律的に支援する次世代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>HR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>インテリジェンス基盤への進化を見据えています。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CTA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Call to Action / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行動喚起）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**CTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（コール・トゥ・アクション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行動喚起）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サイト、ランディングページ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）、アプリケーション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、マーケティング資料などにおいて、訪問者やユーザーに次に取ってほしい具体的なアクション（会員登録、デモ予約、診断開始、購入など）へ導くためのボタン、リンク、または視覚的誘導要素」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>設計の重要ポイント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>明確なアクションラベル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>単なる「送信」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」ではなく、「無料で試してみる」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分で適性診断を開始」「デモ画面を見る」など、クリック後に得られる価値と次のステップが直感的にわかる文言を指定。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高い視覚的コントラスト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ページ内で最も目立つアクセントカラーや適切な余白（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Whitespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を確保し、迷わずクリックできる導線を形成。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>適切な配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ファーストビュー（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>FV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）および価値提案・機能説明セクションの直後に反復配置。</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -21610,7 +22752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E27"/>
+  <dimension ref="B3:E29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -21638,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C27" si="0">C3+1</f>
+        <f t="shared" ref="C4:C29" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -21993,6 +23135,36 @@
         <v>93</v>
       </c>
     </row>
+    <row r="28" spans="2:5" ht="315" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="240" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22001,21 +23173,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="D3"/>
+  <dimension ref="B2:G3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
       <c r="D3" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{519012D9-D57E-4685-BBA6-CB1C8061383A}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{105F50FE-3BAA-4EAE-867D-A196B32BB119}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D77A0B-E2F8-4D45-B63A-949C29728EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD09742-60EE-42AB-979E-B490B2408EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="103">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -22155,6 +22155,10 @@
       </rPr>
       <t>）および価値提案・機能説明セクションの直後に反復配置。</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.2 Learn with ChatGPT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -23173,7 +23177,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="B2:G3"/>
+  <dimension ref="B2:G4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
@@ -23207,6 +23211,11 @@
       </c>
       <c r="G3" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="G4" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD09742-60EE-42AB-979E-B490B2408EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C1A4FE-1E76-4140-B405-928286DFA369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -22159,6 +22159,791 @@
   </si>
   <si>
     <t>1.2 Learn with ChatGPT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SRE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🛠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Site Reliability Engineering / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サイト信頼性エンジニアリング）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（サイト信頼性エンジニアリング）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が提唱したシステム運用の規律・手法であり、ソフトウェア工学（ソフトウェア開発のアプローチ）を用いてインフラ・サービスの可用性、耐障害性、パフォーマンス、スケーラビリティを継続的に向上させる実践体系」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の重要コア概念</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLI / SLO / SLA:
+SLI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（指標）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用性やレスポンス速度の実測値。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（目標）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>チームが目指す信頼性目標（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 99.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（合意）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顧客・ユーザーに対して保証する契約基準。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>トイル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Toil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）の撲滅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>手作業で反復される定常業務を、自動化スクリプトや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CI/CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>パイプラインによって最小化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>障害ポストモーテム（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blameless Postmortem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>障害原因を個人の過失に求めず、システムの構造的欠陥や手順不備を分析して再発防止を図る文化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）における主な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実践</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+DevOps / SRE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>運用仕様書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+docs/DEVOPS_SRE_OPERATION_SPEC.md
+ / 
+docs/SLA_KPI_DEFINITION_AND_MEASUREMENT.md
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用性目標とレスポンス監視の規定。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本の運用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Runbook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>カタログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+docs/OPERATIONS_RUNBOOK_CATALOG.md
+: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>バックアップ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マイグレーション、障害復旧手順を体系化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自動品質・整合性ガード（レーン・プリフライト監査）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>リポジトリのドリフトを即座に機械検知する自動化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>装置。</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -22756,7 +23541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E29"/>
+  <dimension ref="B3:E30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -22784,7 +23569,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C29" si="0">C3+1</f>
+        <f t="shared" ref="C4:C30" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -23169,6 +23954,21 @@
         <v>101</v>
       </c>
     </row>
+    <row r="30" spans="2:5" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C1A4FE-1E76-4140-B405-928286DFA369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81706E12-1C70-432B-80EA-4FA95A015B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -22944,6 +22944,18 @@
       </rPr>
       <t>装置。</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yGCLS7EW91A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://notebook.google.com/notebook/442dbe89-a27d-4b73-a330-4baa0652370c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.3 Check-in</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -23541,7 +23553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E30"/>
+  <dimension ref="B3:E31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -23569,7 +23581,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C30" si="0">C3+1</f>
+        <f t="shared" ref="C4:C31" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -23969,6 +23981,12 @@
         <v>104</v>
       </c>
     </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23977,18 +23995,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="B2:G4"/>
+  <dimension ref="B2:H5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="78.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E2" t="s">
         <v>96</v>
       </c>
@@ -23996,7 +24015,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>1</v>
       </c>
@@ -24009,13 +24028,24 @@
       <c r="E3" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="G3" t="s">
         <v>94</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="G4" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="G5" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -24023,6 +24053,8 @@
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{519012D9-D57E-4685-BBA6-CB1C8061383A}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{105F50FE-3BAA-4EAE-867D-A196B32BB119}"/>
+    <hyperlink ref="H3" r:id="rId3" xr:uid="{F9F88046-A983-43FE-A30C-07771C0C5A43}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{10580E7B-8AA3-47D8-942A-F28AB2887FD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81706E12-1C70-432B-80EA-4FA95A015B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3384C427-AD29-4F0C-9FE0-D7E5AD76B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="113">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -22956,6 +22956,26 @@
   </si>
   <si>
     <t>1.3 Check-in</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.1 What is AI?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QJ-oM6DcMz4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ejHBZzoZxRs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.2 What LLMs can do</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QfyU7N4aVTg</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -23995,7 +24015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="B2:H5"/>
+  <dimension ref="B2:H7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
@@ -24042,10 +24062,29 @@
       <c r="G4" t="s">
         <v>102</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="G5" t="s">
         <v>107</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="G6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="G7" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -24055,6 +24094,9 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{105F50FE-3BAA-4EAE-867D-A196B32BB119}"/>
     <hyperlink ref="H3" r:id="rId3" xr:uid="{F9F88046-A983-43FE-A30C-07771C0C5A43}"/>
     <hyperlink ref="F3" r:id="rId4" xr:uid="{10580E7B-8AA3-47D8-942A-F28AB2887FD5}"/>
+    <hyperlink ref="H4" r:id="rId5" xr:uid="{03BB2B03-8C36-4017-A518-CE3BC314953D}"/>
+    <hyperlink ref="H5" r:id="rId6" xr:uid="{5F2D1BB3-51D2-4792-8A97-B48004C15BAA}"/>
+    <hyperlink ref="H6" r:id="rId7" xr:uid="{1E91F52D-EDCF-444F-A15C-D01E5DA67DFC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3384C427-AD29-4F0C-9FE0-D7E5AD76B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D961B93-EE3D-4870-AAD7-39E9CF2B007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="OpenAIAcademy" sheetId="5" r:id="rId3"/>
     <sheet name="YouTube" sheetId="3" r:id="rId4"/>
     <sheet name="ブログ" sheetId="4" r:id="rId5"/>
+    <sheet name="令和の虎" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -22978,12 +22979,155 @@
     <t>https://www.youtube.com/watch?v=QfyU7N4aVTg</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZFVlTcRwNVU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KWURBiF0kAs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FAL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HEDRA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.3 How models are trained</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.4 Know when to use trusted sources</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5wVvLi-H8PE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VqCeYy7yg28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.5 Why AI needs human review</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Runway</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ElevenLabs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Seedance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Veo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rSjdyQv1Wfc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>【マネ虎だった人々#001マネーの虎　現在の姿［南原社長①］】記念すべき初回ゲストはあの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>‪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@nambara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>‬</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ib7mIx5p7Wo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.6 Check-in</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vLTQ_iJuhho</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.1 Why clear instructions matter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2rzqAjG6Ih8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.2 Task, Concept, and Expectation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Adobe Firefly Services</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Luma Dream Machine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HeyGen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Topaz Video AI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Synthesia</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tavus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shotstack</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23032,6 +23176,12 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -24015,7 +24165,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="B2:H7"/>
+  <dimension ref="B2:J19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
@@ -24023,11 +24173,12 @@
     <col min="4" max="4" width="62.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="78.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="E2" t="s">
         <v>96</v>
       </c>
@@ -24035,7 +24186,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>1</v>
       </c>
@@ -24058,7 +24209,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
       <c r="G4" t="s">
         <v>102</v>
       </c>
@@ -24066,7 +24220,10 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
       <c r="G5" t="s">
         <v>107</v>
       </c>
@@ -24074,7 +24231,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
       <c r="G6" t="s">
         <v>108</v>
       </c>
@@ -24082,9 +24242,156 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
       <c r="G7" t="s">
         <v>111</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="G14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="I15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="I16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I19" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -24097,6 +24404,13 @@
     <hyperlink ref="H4" r:id="rId5" xr:uid="{03BB2B03-8C36-4017-A518-CE3BC314953D}"/>
     <hyperlink ref="H5" r:id="rId6" xr:uid="{5F2D1BB3-51D2-4792-8A97-B48004C15BAA}"/>
     <hyperlink ref="H6" r:id="rId7" xr:uid="{1E91F52D-EDCF-444F-A15C-D01E5DA67DFC}"/>
+    <hyperlink ref="H7" r:id="rId8" xr:uid="{0D564E43-38C4-48F4-AAAB-4525354FC72F}"/>
+    <hyperlink ref="H8" r:id="rId9" xr:uid="{C0D26131-7E05-42BC-82C1-BF5A3C8CA0AA}"/>
+    <hyperlink ref="H9" r:id="rId10" xr:uid="{064DA19D-7439-463F-82FE-C95706338D47}"/>
+    <hyperlink ref="H10" r:id="rId11" xr:uid="{14228D45-42B2-48B7-925F-FA241A01441B}"/>
+    <hyperlink ref="H11" r:id="rId12" xr:uid="{367E638D-234E-4EDB-AEF7-C988D3EC6D19}"/>
+    <hyperlink ref="H12" r:id="rId13" xr:uid="{1F218158-2EA3-4B0C-BF90-D126C575D2B6}"/>
+    <hyperlink ref="H13" r:id="rId14" xr:uid="{4ED2049A-D59E-4607-9BBE-3F4210108A82}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24221,7 +24535,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>46248</v>
       </c>
@@ -24242,4 +24556,34 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C864D64-BD4E-47C2-98A7-786282D674DD}">
+  <dimension ref="B3:D3"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="98.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{2979877C-AB48-4013-966B-133B0CF0552C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D961B93-EE3D-4870-AAD7-39E9CF2B007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D25E2F-FB33-4DF8-B3A4-C308A510F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="142">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -23120,6 +23120,597 @@
   </si>
   <si>
     <t>Shotstack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🛠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Site Reliability Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（サイト信頼性エンジニアリング）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が提唱したシステム運用の規律・手法であり、ソフトウェア工学のアプローチを用いて、インフラ・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サービスの可用性、耐障害性、パフォーマンス、スケーラビリティを継続的に向上・維持させる実践体系」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の重要コア要素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定量的サービスレベル管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+SLI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Indicator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実際の稼働率やレスポンス速度の測定指標。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Objective</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>チームが目指す信頼性目標（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 99.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Agreement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顧客へ保証する契約合意。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>トイル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Toil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）の撲滅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>繰り返される手作業の運用業務を、自動化スクリプトや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CI/CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>パイプラインにより最小化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エラーバジェット（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Error Budget</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>許容される不稼働時間の枠を定義し、新機能リリース速度と安定性のバランスを最適化。</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -24151,10 +24742,16 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
       <c r="C31">
         <f t="shared" si="0"/>
         <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/mighty-link-ai-connect.xlsx
+++ b/mighty-link-ai-connect.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\mighty-link-ai-connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D961B93-EE3D-4870-AAD7-39E9CF2B007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C916C7-DD21-4C33-8943-61B83AF8B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{66EF4EAD-7CE3-414D-A20B-206D64169BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ソースコードレビュー" sheetId="1" r:id="rId1"/>
     <sheet name="用語集" sheetId="2" r:id="rId2"/>
     <sheet name="OpenAIAcademy" sheetId="5" r:id="rId3"/>
-    <sheet name="YouTube" sheetId="3" r:id="rId4"/>
-    <sheet name="ブログ" sheetId="4" r:id="rId5"/>
-    <sheet name="令和の虎" sheetId="6" r:id="rId6"/>
+    <sheet name="Antigravity" sheetId="7" r:id="rId4"/>
+    <sheet name="ClaudeAcademy" sheetId="8" r:id="rId5"/>
+    <sheet name="YouTube" sheetId="3" r:id="rId6"/>
+    <sheet name="ブログ" sheetId="4" r:id="rId7"/>
+    <sheet name="令和の虎" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="193">
   <si>
     <t>C:\Users\kanta\GitHub\mighty-link-ai-connect\__pycache__</t>
     <phoneticPr fontId="1"/>
@@ -16035,10 +16037,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://academy.openai.com/learn/ai-foundations-juzjs/lessons</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -21014,14 +21012,6 @@
       </rPr>
       <t>である「営業マッチング成約時間の削減率」を劇的に改善する中核ターゲット領域となっています。</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1.1 Welcome to AI Foundations</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=yAbco3K_TLQ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -22159,10 +22149,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1.2 Learn with ChatGPT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SRE</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -22945,90 +22931,6 @@
       </rPr>
       <t>装置。</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=yGCLS7EW91A</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://notebook.google.com/notebook/442dbe89-a27d-4b73-a330-4baa0652370c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1.3 Check-in</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.1 What is AI?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=QJ-oM6DcMz4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ejHBZzoZxRs</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2 What LLMs can do</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=QfyU7N4aVTg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ZFVlTcRwNVU</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=KWURBiF0kAs</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FAL</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HEDRA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.3 How models are trained</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.4 Know when to use trusted sources</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=5wVvLi-H8PE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=VqCeYy7yg28</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.5 Why AI needs human review</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Runway</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ElevenLabs</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Seedance</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Veo</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -23071,55 +22973,2592 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=ib7mIx5p7Wo</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🛠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Site Reliability Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+**SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（サイト信頼性エンジニアリング）とは、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が提唱したシステム運用の規律・手法であり、ソフトウェア工学のアプローチを用いて、インフラ・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>サービスの可用性、耐障害性、パフォーマンス、スケーラビリティを継続的に向上・維持させる実践体系」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の重要コア要素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定量的サービスレベル管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+SLI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Indicator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実際の稼働率やレスポンス速度の測定指標。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Objective</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>チームが目指す信頼性目標（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 99.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+SLA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Service Level Agreement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顧客へ保証する契約合意。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>トイル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Toil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）の撲滅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>繰り返される手作業の運用業務を、自動化スクリプトや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CI/CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>パイプラインにより最小化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>エラーバジェット（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Error Budget</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>許容される不稼働時間の枠を定義し、新機能リリース速度と安定性のバランスを最適化。</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2.6 Check-in</t>
+    <t>アドホック</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=vLTQ_iJuhho</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「アドホック（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ad-hoc / Ad hoc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドホックとは、ラテン語で「特定の目的のための」「その場限りの（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>for this purpose only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」を意味し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・ソフトウェア開発分野では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「事前の計画や定型化された手順によらず、その場限りの必要性に応じて臨機応変・単発で作成・実行される処理や対応」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を指します。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代表的な文脈・使われ方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドホッククエリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドホック集計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Ad-hoc Query):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定常的なバッチ処理やダッシュボード画面ではなく、特定のデータ調査・トラブルシューティング・意思決定のためにその都度単発で実行される</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>クエリやスクリプト。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドホックテスト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Ad-hoc Testing):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>定義済みのテスト仕様書（テストケース）に沿わず、エンジニアやテスターが即興的・探索的に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>や機能を触って予期せぬバグを見つけ出すテスト手法。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>アドホック対応（暫定対応</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / Workaround</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>障害発生時や急ぎの仕様変更時に、恒久的なシステム改修の前に一時的に行われる手動操作や暫定パッチ。</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.1 Why clear instructions matter</t>
+    <t>https://www.youtube.com/watch?v=e323zNN2lgI</t>
+  </si>
+  <si>
+    <t>3.3 Review the output</t>
+  </si>
+  <si>
+    <t>〇</t>
+  </si>
+  <si>
+    <t>LUFS</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=2rzqAjG6Ih8</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.2 Task, Concept, and Expectation</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Loudness Units relative to Full Scale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」の解説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（ラウドネス・ユニット・フルスケール）とは、音響・放送・動画配信・音楽制作において</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「人間の耳の聴覚特性（周波数による音の聞こえやすさの偏り）を考慮し、実際に人間が感じる音の大きさ（体感音量）を測定・数値化した国際標準単位（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ITU-R BS.1770 / EBU R128</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS UI Gothic"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>放送規格では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> LKFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Loudness, K-weighted, relative to Full Scale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）とも呼ばれ、実質的に同一の指標です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>なぜ従来の「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>dB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（デシベル）」ではなく「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」を使うのか？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>従来のピークメーター（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>dBFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>音声信号の「電気的な最大振幅」を測るため、瞬間的な一発の破裂音でも高い数値が出ますが、人間が聴いたときの「全体的なうるささ・音圧」とは一致しませんでした。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ラウドネスメーター（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人間の耳が感度の高い中高音域（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4kHz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>付近）を強調するフィルタ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>特性フィルタ）を通し、時間的な平均音圧を測定するため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「実際に聴いたときの音量感」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を正確に統一できます。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代表的な配信プラットフォームのラウドネス基準値</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>各プラットフォームでは、動画や楽曲ごとに急に音が大きくなったり小さくなったりするのを防ぐため、自動ノーマライズ（音量自動調整）を行っています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プラットフォーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>媒体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>基準ラウドネス値</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Target LUFS)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>備考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+YouTube	-14 LUFS	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超過した音声は自動でボリュームが下げられる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Spotify	-14 LUFS	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>標準ノーマライズ設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Apple Music	-16 LUFS	Sound Check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機能の基準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ポッドキャスト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>音声配信</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	-16 LUFS (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ステレオ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>) / -19 LUFS (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>モノラル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>トーク主体の標準推奨値</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>テレビ放送（日本・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ARIB TR-B32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">	-24 LUFS	CM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と番組本編の音量差を規制する基準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>つの測定モード</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Integrated LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（統合ラウドネス）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>音声・動画全体の通算平均音量（マスタリングの最終ターゲット）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Short-term LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（短期ラウドネス）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>直近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>秒間の音量推移。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Momentary LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（瞬間ラウドネス）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>直近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ミリ秒の瞬間的な音量感。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本プロジェクト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mighty Skill-Bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>メディアにおける関連性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>動画デモ・プロモーション動画・ナレーション生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>プロダクト紹介動画や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NotebookLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等による音声解説（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Audio Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を配信する際、リスナーにとって快適で聴き取りやすい音響バランス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">-14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> -16 LUFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を保つための音響マスタリング基準として扱われます。</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Adobe Firefly Services</t>
+  </si>
+  <si>
+    <t>https://antigravity.google/docs/home/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Welcome to Google Antigravity</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Luma Dream Machine</t>
+  </si>
+  <si>
+    <t>OpenAI Academy 学習管理</t>
+  </si>
+  <si>
+    <t>講座リンク、レッスン動画、関連AIツールを用途別に整理</t>
+  </si>
+  <si>
+    <t>講座概要</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>講座名</t>
+  </si>
+  <si>
+    <t>Academy URL</t>
+  </si>
+  <si>
+    <t>YouTube投稿 URL</t>
+  </si>
+  <si>
+    <t>NotebookLM URL</t>
+  </si>
+  <si>
+    <t>1.1 Welcome to AI Foundations</t>
+  </si>
+  <si>
+    <t>https://academy.openai.com/learn/ai-foundations-juzjs/lessons</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yAbco3K_TLQ</t>
+  </si>
+  <si>
+    <t>https://notebook.google.com/notebook/442dbe89-a27d-4b73-a330-4baa0652370c</t>
+  </si>
+  <si>
+    <t>レッスン動画</t>
+  </si>
+  <si>
+    <t>レッスン名</t>
+  </si>
+  <si>
+    <t>YouTube URL</t>
+  </si>
+  <si>
+    <t>NotebookLM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yGCLS7EW91A</t>
+  </si>
+  <si>
+    <t>1.2 Learn with ChatGPT</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QJ-oM6DcMz4</t>
+  </si>
+  <si>
+    <t>1.3 Check-in</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ejHBZzoZxRs</t>
+  </si>
+  <si>
+    <t>2.1 What is AI?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QfyU7N4aVTg</t>
+  </si>
+  <si>
+    <t>2.2 What LLMs can do</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZFVlTcRwNVU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KWURBiF0kAs</t>
+  </si>
+  <si>
+    <t>2.3 How models are trained</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5wVvLi-H8PE</t>
+  </si>
+  <si>
+    <t>2.4 Know when to use trusted sources</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VqCeYy7yg28</t>
+  </si>
+  <si>
+    <t>2.5 Why AI needs human review</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ib7mIx5p7Wo</t>
+  </si>
+  <si>
+    <t>2.6 Check-in</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vLTQ_iJuhho</t>
+  </si>
+  <si>
+    <t>3.1 Why clear instructions matter</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2rzqAjG6Ih8</t>
+  </si>
+  <si>
+    <t>3.2 Task, Concept, and Expectation</t>
+  </si>
+  <si>
+    <t>関連AIツール</t>
+  </si>
+  <si>
+    <t>ツール名</t>
+  </si>
+  <si>
+    <t>確認済み</t>
+  </si>
+  <si>
+    <t>HEDRA</t>
+  </si>
+  <si>
+    <t>FAL</t>
+  </si>
+  <si>
+    <t>Runway</t>
+  </si>
+  <si>
+    <t>ElevenLabs</t>
+  </si>
+  <si>
+    <t>Seedance</t>
+  </si>
+  <si>
+    <t>Veo</t>
+  </si>
+  <si>
+    <t>HeyGen</t>
+  </si>
+  <si>
+    <t>Topaz Video AI</t>
+  </si>
+  <si>
+    <t>Synthesia</t>
+  </si>
+  <si>
+    <t>Tavus</t>
+  </si>
+  <si>
+    <t>Shotstack</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pKfb0oox3_8</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HeyGen</t>
+    <t>https://notebook.google.com/notebook/bf99897b-fe4d-474e-a25b-22f3bd1da24f</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Topaz Video AI</t>
+    <t>Antigravity 2.0</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Synthesia</t>
+    <t>https://antigravity.google/docs/overview/</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Tavus</t>
+    <t>Google Flow</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Shotstack</t>
+    <t>サブスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Welcome to Claude Academy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.claude.com/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4rxcDyniuNw</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.claude.com/ja/courses/claude-code-101</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Claude Code 101</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://notebook.google.com/notebook/4ab6b6f9-5fe9-4073-9a53-85321260807b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Pe-2A1Rq6Hc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Getting Started with Antigravity 2.0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://antigravity.google/docs/getting-started/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.claude.com/ja/courses/claude-code-101/what-is-claude-code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Claude Codeとは？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BjOtCEYRzmc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.claude.com/ja/courses/claude-code-101/how-claude-code-works</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Claude Codeの仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI大学</t>
+    <rPh sb="2" eb="4">
+      <t>ダイガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://academy.claude.com/ja/courses/claude-code-101/installing-claude-code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Claude Codeのインストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wqjrEI6GcYE</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -23127,7 +25566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23183,13 +25622,59 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS UI Gothic"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -23209,7 +25694,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -23222,12 +25707,113 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -23238,6 +25824,45 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F3C1F5F-7B96-42FA-AE6C-FCDEA3288098}" name="OpenAIAcademyOverview" displayName="OpenAIAcademyOverview" ref="A4:E5" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A4:E5" xr:uid="{4F3C1F5F-7B96-42FA-AE6C-FCDEA3288098}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{EB1159DB-4DFE-4D42-AF05-DA1405FC8D97}" name="No." dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{66ABA36C-6198-4013-964A-D8514779FE6E}" name="講座名" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{7E592AD6-6191-4740-AA50-AB5A546AA082}" name="Academy URL" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{5EB4DC8E-DCEA-40A7-94FE-1257F53672C2}" name="YouTube投稿 URL" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{773821AD-4E74-4982-A268-36D7B5B061EE}" name="NotebookLM URL" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E690145-DFD4-4608-B746-B8BC87AAEC0B}" name="OpenAIAcademyLessons" displayName="OpenAIAcademyLessons" ref="A8:D21" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A8:D21" xr:uid="{5E690145-DFD4-4608-B746-B8BC87AAEC0B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6AA3F78C-DA07-46F2-860F-03A202FEA960}" name="No." dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{72690B91-8717-4401-A620-375C4A4CF651}" name="レッスン名" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{DF1DC285-847F-4B9C-91F1-48BD62111A11}" name="YouTube URL" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{669A9F1A-DAF8-48C6-898B-396F9166EF9E}" name="NotebookLM" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1705A361-A975-42B5-ABF7-C5EB161CB3D0}" name="OpenAIAcademyTools" displayName="OpenAIAcademyTools" ref="A24:C38" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A24:C38" xr:uid="{1705A361-A975-42B5-ABF7-C5EB161CB3D0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0BD1BA68-9FC1-4B0F-9467-16FCF66D49D3}" name="ツール名" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{3D1F0461-BB36-47B2-A727-7B1226345334}" name="確認済み" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5BAF893C-F8A2-442E-87F6-9737E05D3C0F}" name="サブスク" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23723,7 +26348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61D7BD1-E21E-491C-9734-845F33AEBE13}">
-  <dimension ref="B3:E31"/>
+  <dimension ref="B3:E33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3.375" bestFit="1" customWidth="1"/>
@@ -23751,7 +26376,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C31" si="0">C3+1</f>
+        <f t="shared" ref="C4:C33" si="0">C3+1</f>
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -23983,7 +26608,7 @@
         <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="367.5" x14ac:dyDescent="0.4">
@@ -23998,7 +26623,7 @@
         <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
@@ -24010,10 +26635,10 @@
         <v>19</v>
       </c>
       <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="333.75" x14ac:dyDescent="0.4">
@@ -24025,10 +26650,10 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
@@ -24040,10 +26665,10 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="307.5" x14ac:dyDescent="0.4">
@@ -24055,10 +26680,10 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="240" x14ac:dyDescent="0.4">
@@ -24070,10 +26695,10 @@
         <v>23</v>
       </c>
       <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
@@ -24085,10 +26710,10 @@
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="236.25" x14ac:dyDescent="0.4">
@@ -24100,10 +26725,10 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="315" x14ac:dyDescent="0.4">
@@ -24115,10 +26740,10 @@
         <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="240" x14ac:dyDescent="0.4">
@@ -24130,10 +26755,10 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="409.5" x14ac:dyDescent="0.4">
@@ -24145,16 +26770,46 @@
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
       <c r="C31">
         <f t="shared" si="0"/>
         <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="258.75" x14ac:dyDescent="0.4">
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -24165,11 +26820,474 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49199C90-9BB8-45C0-BAA3-6AD72AA42C11}">
-  <dimension ref="B2:J19"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="78.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="5">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="5">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A14" s="5">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A15" s="5">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A16" s="5">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A17" s="5">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="5">
+        <v>10</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="5">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="5">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="5">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A23" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="B25:B38">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"〇"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D21">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"〇"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06BEF523-B434-4C32-9B44-37C4DE1DAAF0}">
+  <dimension ref="B2:H15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="78.75" bestFit="1" customWidth="1"/>
@@ -24178,245 +27296,280 @@
     <col min="9" max="9" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>105</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B4">
+        <f>B3+1</f>
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B5">
+        <f>B4+1</f>
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="F5" t="s">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F6" t="s">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F7" t="s">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" t="s">
-        <v>116</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
+      <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F8" t="s">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" t="s">
-        <v>115</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
+      <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F9" t="s">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
+      <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F10" t="s">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
+      <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F11" t="s">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" t="s">
-        <v>124</v>
-      </c>
-      <c r="J11" t="s">
-        <v>1</v>
-      </c>
+      <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F12" t="s">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" t="s">
-        <v>125</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1</v>
-      </c>
+      <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F13" t="s">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" t="s">
-        <v>134</v>
-      </c>
+      <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="G14" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" t="s">
-        <v>135</v>
-      </c>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="I15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J15" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F15" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="I16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.4">
-      <c r="I17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.4">
-      <c r="I18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
-      <c r="I19" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{519012D9-D57E-4685-BBA6-CB1C8061383A}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{105F50FE-3BAA-4EAE-867D-A196B32BB119}"/>
-    <hyperlink ref="H3" r:id="rId3" xr:uid="{F9F88046-A983-43FE-A30C-07771C0C5A43}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{10580E7B-8AA3-47D8-942A-F28AB2887FD5}"/>
-    <hyperlink ref="H4" r:id="rId5" xr:uid="{03BB2B03-8C36-4017-A518-CE3BC314953D}"/>
-    <hyperlink ref="H5" r:id="rId6" xr:uid="{5F2D1BB3-51D2-4792-8A97-B48004C15BAA}"/>
-    <hyperlink ref="H6" r:id="rId7" xr:uid="{1E91F52D-EDCF-444F-A15C-D01E5DA67DFC}"/>
-    <hyperlink ref="H7" r:id="rId8" xr:uid="{0D564E43-38C4-48F4-AAAB-4525354FC72F}"/>
-    <hyperlink ref="H8" r:id="rId9" xr:uid="{C0D26131-7E05-42BC-82C1-BF5A3C8CA0AA}"/>
-    <hyperlink ref="H9" r:id="rId10" xr:uid="{064DA19D-7439-463F-82FE-C95706338D47}"/>
-    <hyperlink ref="H10" r:id="rId11" xr:uid="{14228D45-42B2-48B7-925F-FA241A01441B}"/>
-    <hyperlink ref="H11" r:id="rId12" xr:uid="{367E638D-234E-4EDB-AEF7-C988D3EC6D19}"/>
-    <hyperlink ref="H12" r:id="rId13" xr:uid="{1F218158-2EA3-4B0C-BF90-D126C575D2B6}"/>
-    <hyperlink ref="H13" r:id="rId14" xr:uid="{4ED2049A-D59E-4607-9BBE-3F4210108A82}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{D7A01C7E-D543-411B-B28A-F0C4B2147C84}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{D67DD94E-D8FA-4E8C-ACF1-A6C812EED56C}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{5768FE47-DF4C-4128-9AF7-CA0B6A568B07}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{9BCEC014-F93D-47D8-9FAE-4A1DA92B19D9}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{C0B5B1BE-153B-420B-B3F4-693F65193819}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{3AC3A764-8357-466F-9958-56623369F1E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADA3461-3FC5-4E21-A085-8E75E91C0BA9}">
+  <dimension ref="B2:G7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B4">
+        <f>B3+1</f>
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B5">
+        <f>B4+1</f>
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B6">
+        <f>B5+1</f>
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B7">
+        <f>B6+1</f>
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{137CE8D7-B230-441C-A546-6C7A3A25674F}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{CF32CD14-EA3C-433E-88FE-13FB85693333}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{027C4A4C-AC0D-4CF8-8730-225F983CA595}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{9E41268E-7F13-4BD7-8F0B-64F329BDBE7D}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{96172731-C12D-4AED-B7A7-9283CCA8E687}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{05CDA43B-635F-4E60-9722-DE1AFB891F50}"/>
+    <hyperlink ref="E5" r:id="rId7" xr:uid="{242195AF-69F3-4D62-89CC-02A48B20D497}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{93488C18-17D5-4AA3-BDD3-DF6E45591AD2}"/>
+    <hyperlink ref="E6" r:id="rId9" xr:uid="{7131FFA0-BABE-4EB1-A5BC-2EF10BF8B3E1}"/>
+    <hyperlink ref="D7" r:id="rId10" xr:uid="{F2481D20-8F5F-448C-B8AF-2B038779C9B1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFF1E46-B8F1-4111-9292-CB57C462E366}">
   <dimension ref="A2:F6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -24520,7 +27673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3130DC33-D7DC-49CA-BAC6-4FF425438F8A}">
   <dimension ref="A2:D3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -24558,7 +27711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C864D64-BD4E-47C2-98A7-786282D674DD}">
   <dimension ref="B3:D3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -24573,10 +27726,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
